--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T16:28:32+02:00</t>
+    <t>2025-08-18T11:20:46+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-18T11:20:46+02:00</t>
+    <t>2025-08-26T14:51:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T14:51:56+02:00</t>
+    <t>2025-09-10T16:13:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T16:13:27+02:00</t>
+    <t>2025-09-12T12:04:03+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T12:04:03+02:00</t>
+    <t>2025-09-12T14:17:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-patient.xlsx
+++ b/StructureDefinition-chul-patient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T14:17:00+02:00</t>
+    <t>2026-02-04T18:27:09+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
